--- a/output/full_scan/batch_seq7_2026-10-13.xlsx
+++ b/output/full_scan/batch_seq7_2026-10-13.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>72.60027765121519</v>
+        <v>72.60027769066207</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>25.10023034948535</v>
+        <v>25.10023041700325</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.928327052123581</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.379517279075846</v>
+        <v>1.379517279027774</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>80.06290310721855</v>
+        <v>80.0629031688413</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>62.18642291651666</v>
+        <v>62.18642298546592</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2.275344133263122</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.075671008793693</v>
+        <v>2.075671008493255</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67.06603859570588</v>
+        <v>67.06603861445194</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>29.87635481739732</v>
+        <v>29.87635493022318</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1.348355806221929</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>5.219085450529128</v>
+        <v>5.219085450048404</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>62.58281528066424</v>
+        <v>62.58281538737848</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15.36382486166943</v>
+        <v>15.36382495509064</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>2.926259743095039</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.6396008834937739</v>
+        <v>0.6396008830851809</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>67.37339360030543</v>
+        <v>67.37339359173301</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>37.74698327080829</v>
+        <v>37.74698329270634</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>5.155200927455402</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.5250079868046387</v>
+        <v>0.525007986708499</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>77.99410921414837</v>
+        <v>77.99410922369164</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>48.3436640773178</v>
+        <v>48.34366415242705</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.727596584355506</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>3.732627328886736</v>
+        <v>3.73262732876656</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>998.6966910382728</v>
+        <v>998.6966910382736</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>14.3</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>66.49137323493596</v>
+        <v>66.49137326576037</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>24.14552192448608</v>
+        <v>24.14552193252419</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>2.222231464975465</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>60.97449898964112</v>
+        <v>60.97449900581832</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>13.31673580362799</v>
+        <v>13.31673586157779</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>2.527894660786612</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1649184500494349</v>
+        <v>0.1649184500374184</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>79.66056282850485</v>
+        <v>79.66056293186068</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>53.10830497650527</v>
+        <v>53.1083050924002</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2.57787803208491</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.8719851168825485</v>
+        <v>0.8719851164859755</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>60.35148679675648</v>
+        <v>60.35148682583997</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>43.82484323215901</v>
+        <v>43.82484335446454</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1.696277519646755</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.1766001548904485</v>
+        <v>-0.1766001551067457</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>61.46442206438165</v>
+        <v>61.46442211758048</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>36.59476664823696</v>
+        <v>36.59476677127697</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.587123473745553</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>2.885714585507575</v>
+        <v>2.885714584786556</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>881.1084462520272</v>
+        <v>881.1084462520271</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>283.5</v>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>70.61330636808029</v>
+        <v>70.61330644088426</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38.8344871267509</v>
+        <v>38.8344871167035</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.29468331688535</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>3.548385643172736</v>
+        <v>3.54838564209122</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.22951330618683</v>
+        <v>65.2295134343801</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45.70548863160248</v>
+        <v>45.7054886751739</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>2.362926280526636</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.342404095249925</v>
+        <v>1.342404093807868</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58.30662292232546</v>
+        <v>58.30662302758589</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>35.26497553530479</v>
+        <v>35.26497570034384</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.802670517730528</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-5.410181597843312</v>
+        <v>-5.410181604092252</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.04835181508987</v>
+        <v>57.04835190218034</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>28.61248782224641</v>
+        <v>28.61248798755653</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.113381799849138</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.9326444531664536</v>
+        <v>-0.9326444544883294</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>747.8406832599535</v>
+        <v>747.8406832599538</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>313</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>48.21068804461471</v>
+        <v>48.21068839584106</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>19.81047032494452</v>
+        <v>19.81047032866121</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>2.023982633036459</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.3991041868227714</v>
+        <v>0.3991041846596834</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>69.42489015929318</v>
+        <v>69.42489067554895</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>41.54321469575128</v>
+        <v>41.54321472456944</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.3664863214310157</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0137447241106485</v>
+        <v>0.0137447239183731</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>52.17327680221867</v>
+        <v>52.17327684105463</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>21.92377546066227</v>
+        <v>21.92377562607231</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.5606312736988097</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-10.73964461855805</v>
+        <v>-10.73964462817225</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>54.63140610960876</v>
+        <v>54.63140617233567</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>32.83562031339452</v>
+        <v>32.83562045191292</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0.8582373129765331</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>7.328340710288337</v>
+        <v>7.328340706683171</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>720.0517602067619</v>
+        <v>720.0517602067608</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>62.9</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>69.99386029482368</v>
+        <v>69.99386049868832</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>54.41844044826065</v>
+        <v>54.41844044003722</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>3.788199491631269</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.6976475574080654</v>
+        <v>0.6976475567351006</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>698.7671858020859</v>
+        <v>698.7671858020874</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>93.3</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>56.22732317207272</v>
+        <v>56.22732375843429</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>24.43959128343645</v>
+        <v>24.43959134646304</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.10509646259264</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.4327359834779767</v>
+        <v>0.4327359839586635</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>46.59008949698418</v>
+        <v>46.59008950988886</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>38.31780667517356</v>
+        <v>38.31780672317568</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.992160399704914</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-15.49342048622903</v>
+        <v>-15.49342048661356</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>687.121606378669</v>
+        <v>687.1216063786705</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>33.25</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.63711234877528</v>
+        <v>57.63711255158432</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>27.6873998077301</v>
+        <v>27.68739981378699</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.6756143552924805</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.1079171143450632</v>
+        <v>0.1079171142969939</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>57.71479763239672</v>
+        <v>57.71479776067611</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>27.26920087652557</v>
+        <v>27.26920092014896</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>1.941404829415261</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.3706804994536739</v>
+        <v>0.3706804992373665</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46.93713087551248</v>
+        <v>46.93713096041285</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>33.16414165169764</v>
+        <v>33.16414181157378</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>0.6913135212305275</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-37.93623596121577</v>
+        <v>-37.93623597323315</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>53.98999569020118</v>
+        <v>53.98999573769578</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>51.0689783421403</v>
+        <v>51.06897850303594</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>0.3045473314225146</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.8823520102590532</v>
+        <v>-0.8823520106436149</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.89685785304106</v>
+        <v>56.89685796376401</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>36.346711145313</v>
+        <v>36.34671141671436</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.3528437263809809</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.4590796973209734</v>
+        <v>-0.459079698042026</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>632.0884576584541</v>
+        <v>632.0884576584539</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>365.5</v>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>52.00242166303397</v>
+        <v>52.00242181945056</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>19.72607834717454</v>
+        <v>19.72607854262202</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.6627351892236804</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.129702375266323</v>
+        <v>1.129702372502387</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>55.43214838229026</v>
+        <v>55.4321484379675</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>19.50884900707723</v>
+        <v>19.50884905950642</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>1.157399452091362</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.4560654831786892</v>
+        <v>-0.4560654835392119</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6743</v>
+        <v>6533</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>584.0024005704888</v>
+        <v>606.9986313552256</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>32.25</v>
+        <v>317</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>54.63021037062671</v>
+        <v>56.05861275336537</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>36.92184394150474</v>
+        <v>35.30169383576973</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.9826428720016692</v>
+        <v>0.3320987716306312</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0198711602835679</v>
+        <v>2.62449129819899</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6792</v>
+        <v>6743</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>578.5419716355019</v>
+        <v>584.0024005704888</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>59.4</v>
+        <v>32.25</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>50.68385021516569</v>
+        <v>54.63021053992206</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>34.4901615177895</v>
+        <v>36.92184401254347</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.9085208016438502</v>
+        <v>0.9826428720016692</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.071091320995054</v>
+        <v>0.0198711600912901</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6643</v>
+        <v>6792</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>569.500600842875</v>
+        <v>578.5419716355019</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>458</v>
+        <v>59.4</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46.34171410426634</v>
+        <v>50.68385005790593</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>31.65536915290542</v>
+        <v>34.49016160594108</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7599356721798803</v>
+        <v>0.9085208016438502</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-4.892649019047109</v>
+        <v>0.071091320995054</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6756</v>
+        <v>6643</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>566.6356559354222</v>
+        <v>569.500600842875</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>96.40000000000001</v>
+        <v>458</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,49 +2248,49 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45.6581499909534</v>
+        <v>46.34171412524553</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>14.01473011708947</v>
+        <v>31.6553691836308</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2.016999019287349</v>
+        <v>0.7599356721798803</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.0985491768520316</v>
+        <v>-4.892649020729536</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6768</v>
+        <v>6756</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>563.3921007887794</v>
+        <v>566.6356559354222</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>63.9</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>50.508491050589</v>
+        <v>45.65815034879874</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.68320677002004</v>
+        <v>14.01473031448901</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.714210743309571</v>
+        <v>2.016999019287349</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.337136918296514</v>
+        <v>-0.09854917745290249</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6716</v>
+        <v>6768</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>561.6623415594348</v>
+        <v>563.3921007887798</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>112.5</v>
+        <v>63.9</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>43.54635721079964</v>
+        <v>50.50849099918221</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>32.45288900635988</v>
+        <v>22.68320675948403</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2.483729361054434</v>
+        <v>0.714210743309571</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.0410750523346621</v>
+        <v>0.3371369184166831</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6763</v>
+        <v>6716</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>551.4080730189125</v>
+        <v>561.6623415594347</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>41.1</v>
+        <v>112.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45.04972117896646</v>
+        <v>43.54635722285359</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>16.37231910245754</v>
+        <v>32.45288911094951</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.278764023639442</v>
+        <v>2.483729361054434</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0464777182470041</v>
+        <v>-0.041075052599047</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6641</v>
+        <v>6763</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>550.0429727477983</v>
+        <v>551.4080730189213</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>17.25</v>
+        <v>41.1</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>52.08940430478288</v>
+        <v>45.04972177759212</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>8.279930641705354</v>
+        <v>16.3723190083272</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.339577805975315</v>
+        <v>1.278764023639442</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1298128952657475</v>
+        <v>0.0464777179105141</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6654</v>
+        <v>6641</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>538.3044670050058</v>
+        <v>550.0429727477983</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>209.5</v>
+        <v>17.25</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>53.2380076254073</v>
+        <v>52.08940430868481</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>31.03825102350362</v>
+        <v>8.27993076880502</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.763077010482061</v>
+        <v>1.339577805975315</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>1</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.3579778586269864</v>
+        <v>0.1298128952897817</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6530</v>
+        <v>6654</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>533.7371431660036</v>
+        <v>538.3044670050059</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>91.3</v>
+        <v>209.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>43.54087954728918</v>
+        <v>53.23800763748019</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>27.93794359247613</v>
+        <v>31.03825105989027</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3201187998722429</v>
+        <v>1.763077010482061</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,48 +2584,48 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.33912843710998</v>
+        <v>-0.3579778588192592</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6806</v>
+        <v>6530</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>533.7371431660036</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>3.51</v>
+        <v>91.3</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="G41" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>31.69496066993881</v>
+        <v>43.54087971420449</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>32.59380893356278</v>
+        <v>27.9379439329882</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.3201187998722429</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,51 +2637,51 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.4112811360301456</v>
+        <v>-1.339128438191531</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6577</v>
+        <v>6806</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>527.1529555970369</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>79.8</v>
+        <v>3.51</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G42" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>48.52706721178018</v>
+        <v>31.694993700715</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>11.05258291613535</v>
+        <v>32.59379607878951</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.470658959788392</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0304824432162078</v>
+        <v>0.4112809649420565</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6693</v>
+        <v>6577</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>512.5551235220297</v>
+        <v>527.1529555970369</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>185.5</v>
+        <v>79.8</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45.93554910758656</v>
+        <v>48.52706722229504</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>23.07377337716659</v>
+        <v>11.05258298525289</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6884510989420659</v>
+        <v>1.470658959788392</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-1.549031306611443</v>
+        <v>0.0304824431200758</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6835</v>
+        <v>6693</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>512.4380966612196</v>
+        <v>512.5551235220297</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>31.6</v>
+        <v>185.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.74765442688766</v>
+        <v>45.93554910589792</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.67126795711365</v>
+        <v>23.07377327073059</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.768418128556517</v>
+        <v>0.6884510989420659</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1138554341838084</v>
+        <v>-1.549031306587452</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6655</v>
+        <v>6835</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>509.0806671800955</v>
+        <v>512.4380966612007</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>127</v>
+        <v>31.6</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>52.22676383686791</v>
+        <v>51.74765447994901</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10.34499489954325</v>
+        <v>22.67126797499167</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2088952116910577</v>
+        <v>0.768418128556517</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>3.528194684984556</v>
+        <v>0.1138554342559143</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6485</v>
+        <v>6655</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>496.7648971741625</v>
+        <v>509.0806671800955</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>76.5</v>
+        <v>127</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>55.92390110588602</v>
+        <v>52.2267638419452</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>37.41958231503138</v>
+        <v>10.34499490413343</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6433027820635637</v>
+        <v>0.2088952116910577</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>1</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.4867790370023837</v>
+        <v>3.528194684744208</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6689</v>
+        <v>6485</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>490.9379642551559</v>
+        <v>496.7648971741625</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>51.57597415637712</v>
+        <v>55.92390117041391</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>23.1925366346656</v>
+        <v>37.41958243072551</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2297310802463042</v>
+        <v>0.6433027820635637</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.2117315894912395</v>
+        <v>0.4867790365697555</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6570</v>
+        <v>6689</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>488.3773366456109</v>
+        <v>490.9379642551559</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>46.4</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>35.11241753659655</v>
+        <v>51.57597433708567</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>18.52856581979152</v>
+        <v>23.19253670124465</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.875937659849383</v>
+        <v>0.2297310802463042</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.1457377934493537</v>
+        <v>-0.2117315900440288</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6831</v>
+        <v>6570</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>485.4407320426817</v>
+        <v>488.3773366456109</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>478.5</v>
+        <v>46.4</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>38.24842212704057</v>
+        <v>35.11241761538237</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>26.45120767366401</v>
+        <v>18.52856594508953</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.9308086661156848</v>
+        <v>2.875937659849383</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>2.220682269127568</v>
+        <v>0.1457377934012871</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6757</v>
+        <v>6831</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>477.9887505710825</v>
+        <v>485.4407320426795</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>53.4</v>
+        <v>478.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,49 +3096,49 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>44.0390035831715</v>
+        <v>38.24842216295461</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14.70521533311959</v>
+        <v>26.45120775828064</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7033222825318546</v>
+        <v>0.9308086661156848</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0720291742713484</v>
+        <v>2.220682267925796</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6556</v>
+        <v>6757</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>474.6710644380919</v>
+        <v>477.9887505710825</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>62</v>
+        <v>53.4</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>52.48755376503063</v>
+        <v>44.0390035831715</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>11.03746629735226</v>
+        <v>14.70521538160918</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.007566133261573</v>
+        <v>0.7033222825318546</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.140087857945736</v>
+        <v>0.0720291742473155</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6790</v>
+        <v>6556</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>473.9057588570615</v>
+        <v>474.671064438092</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>37.7</v>
+        <v>62</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>49.65035344323928</v>
+        <v>52.48755379214449</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.74007459158051</v>
+        <v>11.03746637373441</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.161672051090212</v>
+        <v>1.007566133261573</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0073358899585609</v>
+        <v>0.1400878576813601</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6591</v>
+        <v>6790</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>473.6728143627487</v>
+        <v>473.9057588570615</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>43.3</v>
+        <v>37.7</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.82070031944945</v>
+        <v>49.65035353276912</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>29.59081683993079</v>
+        <v>20.74007461470302</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.9599531572516196</v>
+        <v>1.161672051090212</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.009555445604283499</v>
+        <v>0.0073358899465446</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6531</v>
+        <v>6591</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>473.6327798090059</v>
+        <v>473.6728143628902</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>926</v>
+        <v>43.3</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,49 +3308,49 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>46.51118363331179</v>
+        <v>51.82069961826077</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>13.84086891245406</v>
+        <v>29.59081721764833</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2.263277980900592</v>
+        <v>0.9599531572516196</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-5.887555508279231</v>
+        <v>-0.0095554445707917</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6683</v>
+        <v>6531</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>468.2241774831563</v>
+        <v>473.6327798090059</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1370</v>
+        <v>926</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>44.94876091002772</v>
+        <v>46.51118364610374</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>15.10429919458038</v>
+        <v>13.84086898627044</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5442819574456194</v>
+        <v>2.263277980900592</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-26.80322386372677</v>
+        <v>-5.88755550912046</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6614</v>
+        <v>6683</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>467.315463023072</v>
+        <v>468.2241774831563</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>35.05</v>
+        <v>1370</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,49 +3414,49 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>40.04577040787257</v>
+        <v>44.94876094152958</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.90729885279871</v>
+        <v>15.10429924298355</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.196323734857891</v>
+        <v>0.5442819574456194</v>
       </c>
       <c r="K56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M56" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0003397841318302</v>
+        <v>-26.80322386781277</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6669</v>
+        <v>6614</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>467.0379655026094</v>
+        <v>467.315463023074</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>2195</v>
+        <v>35.05</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>31.83699443245592</v>
+        <v>40.04576992971227</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>42.49148683905894</v>
+        <v>21.90729892782694</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8334510711967095</v>
+        <v>1.196323734857891</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>148.0570451093843</v>
+        <v>0.0003397842760343</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6657</v>
+        <v>6669</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>466.8000881224802</v>
+        <v>467.0379655026094</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>33.25</v>
+        <v>2195</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>50.77841939518898</v>
+        <v>31.83699456568984</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>23.90465568637084</v>
+        <v>42.49148702558927</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.154489454343749</v>
+        <v>0.8334510711967095</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0043034077706981</v>
+        <v>148.057045032474</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6670</v>
+        <v>6657</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>465.3052946424827</v>
+        <v>466.8000881224802</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>266</v>
+        <v>33.25</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,49 +3573,49 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>41.92678951760824</v>
+        <v>50.77841962536409</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>17.99198881120364</v>
+        <v>23.90465564632015</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.497636416467225</v>
+        <v>1.154489454343749</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.4848776279371831</v>
+        <v>-0.0043034081312194</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, invest_trust_buy_2d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6550</v>
+        <v>6670</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>452.3318494102415</v>
+        <v>465.3052946424828</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>15.9</v>
+        <v>266</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,49 +3626,49 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>64.50070565142146</v>
+        <v>41.92678948012357</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>35.1443562736703</v>
+        <v>17.991988656741</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4522062633235976</v>
+        <v>1.497636416467225</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2760034727760452</v>
+        <v>-0.4848776274564876</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6830</v>
+        <v>6550</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>452.2054404227747</v>
+        <v>452.3318494102415</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>520</v>
+        <v>15.9</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>46.62829355670814</v>
+        <v>64.5007048410836</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>22.02401360408759</v>
+        <v>35.14435793181482</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7900982631867427</v>
+        <v>0.4522062633235976</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-5.120674496375972</v>
+        <v>0.2760034742444324</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6525</v>
+        <v>6830</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>451.7282339845052</v>
+        <v>452.2054404227747</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>133.5</v>
+        <v>520</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45.21439857859973</v>
+        <v>46.62829359398743</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>13.2396959121042</v>
+        <v>22.02401372988847</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6735826177666991</v>
+        <v>0.7900982631867427</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.5326661164704303</v>
+        <v>-5.12067449817858</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6498</v>
+        <v>6525</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>445.783348770987</v>
+        <v>451.7282339845056</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>133.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>50.47288071983001</v>
+        <v>45.21439862279968</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>16.91656982842723</v>
+        <v>13.23969600469517</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.597218995214976</v>
+        <v>0.6735826177666991</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.7493335977346223</v>
+        <v>0.5326661162541351</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6741</v>
+        <v>6498</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>430.978573358151</v>
+        <v>445.7833487709867</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>53.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>29.84925522514661</v>
+        <v>50.47288087583785</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>31.31402394320263</v>
+        <v>16.91656980979198</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.542441502932658</v>
+        <v>1.597218995214976</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.2779034047237175</v>
+        <v>0.7493335967732483</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6640</v>
+        <v>6741</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>429.957707713386</v>
+        <v>430.9785733581508</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>1080</v>
+        <v>53.8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>48.48681585964561</v>
+        <v>29.84925545154596</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>19.92201570360636</v>
+        <v>31.31402384557295</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.9864653607912786</v>
+        <v>1.542441502932658</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-2.45974047774309</v>
+        <v>-0.277903405228436</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6776</v>
+        <v>6640</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>428.4219263865937</v>
+        <v>429.957707713386</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>52.4</v>
+        <v>1080</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>46.98578377980481</v>
+        <v>48.48681590257508</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>12.42896592867051</v>
+        <v>19.92201589681509</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.327923921713341</v>
+        <v>0.9864653607912786</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0907871921878082</v>
+        <v>-2.459740483992189</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6829</v>
+        <v>6776</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>416.7939571697255</v>
+        <v>428.4219263865937</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>201</v>
+        <v>52.4</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>41.51195401586799</v>
+        <v>46.985783823923</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9.730078496321353</v>
+        <v>12.4289658163604</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.073475537306291</v>
+        <v>1.327923921713341</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.647012089113276</v>
+        <v>0.0907871921878082</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6605</v>
+        <v>6829</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>411.6673814081736</v>
+        <v>416.7939571697255</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>135.5</v>
+        <v>201</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45.1664510868674</v>
+        <v>41.51195406187325</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.60251176463187</v>
+        <v>9.730078531159595</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.8971949918673509</v>
+        <v>1.073475537306291</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.2970303992931712</v>
+        <v>-0.6470120900746599</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6584</v>
+        <v>6605</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>411.5234567324944</v>
+        <v>411.6673814081736</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>493.5</v>
+        <v>135.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>33.13611067023893</v>
+        <v>45.16645122651539</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>18.95731739151401</v>
+        <v>10.60251183687171</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.047208510337542</v>
+        <v>0.8971949918673509</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-3.280340593531005</v>
+        <v>-0.2970303998940584</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6684</v>
+        <v>6584</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>410.77324022608</v>
+        <v>411.5234567324944</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>46.5</v>
+        <v>493.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>40.92991838762968</v>
+        <v>33.13611071628875</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>24.42544703362157</v>
+        <v>18.95731746170578</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6234309103126643</v>
+        <v>1.047208510337542</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.2593186263540902</v>
+        <v>-3.280340596895736</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6585</v>
+        <v>6684</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>410.0699156658477</v>
+        <v>410.7732402260736</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>98</v>
+        <v>46.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>30.91764801262958</v>
+        <v>40.92991848346821</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>33.55546441774346</v>
+        <v>24.42544715150353</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.749388543640967</v>
+        <v>0.6234309103126643</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.2289553945968165</v>
+        <v>-0.2593186267146054</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6799</v>
+        <v>6585</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>402.8627845105019</v>
+        <v>410.0699156658474</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>86.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>50.09757666182077</v>
+        <v>30.91764809829198</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>31.35599279210424</v>
+        <v>33.55546448792384</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4323379976841194</v>
+        <v>1.749388543640967</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.0508540262774834</v>
+        <v>-0.2289553949813747</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6823</v>
+        <v>6799</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>394.1020338470789</v>
+        <v>402.8627845105019</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>60.8</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>50.50427501666378</v>
+        <v>50.0975768587035</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19.4500545042685</v>
+        <v>31.35599288766347</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.560953443459568</v>
+        <v>0.4323379976841194</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.08906582801810251</v>
+        <v>-0.0508540269744788</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6735</v>
+        <v>6823</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>392.7772159702823</v>
+        <v>394.1020338470789</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>59.7</v>
+        <v>60.8</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>36.81333958315828</v>
+        <v>50.50427534663237</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>20.49202944746008</v>
+        <v>19.45005463485878</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.599418216383708</v>
+        <v>1.560953443459568</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.3237281942221388</v>
+        <v>0.089065826551989</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6789</v>
+        <v>6735</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>387.8375177783666</v>
+        <v>392.7772159702827</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>453.5</v>
+        <v>59.7</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,49 +4421,49 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.33411253061785</v>
+        <v>36.81333967708753</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>17.10409459497794</v>
+        <v>20.49202945335606</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.171090698818906</v>
+        <v>1.599418216383708</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-1.526786422113266</v>
+        <v>-0.3237281941981112</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6560</v>
+        <v>6789</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>381.7486766922588</v>
+        <v>387.8375177783684</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>32.6</v>
+        <v>453.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,49 +4474,49 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>51.00802427251625</v>
+        <v>43.33411267325646</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>11.84296414176933</v>
+        <v>17.10409474929508</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3518345682055275</v>
+        <v>1.171090698818906</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M76" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0471317499938783</v>
+        <v>-1.526786427521094</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6582</v>
+        <v>6560</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>376.3444454967212</v>
+        <v>381.7486766922593</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>31.5</v>
+        <v>32.6</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>49.97313136240614</v>
+        <v>51.0080242500747</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>16.11337860436831</v>
+        <v>11.84296430897575</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5924827903738391</v>
+        <v>0.3518345682055275</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0858805125663497</v>
+        <v>-0.0471317498616893</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6588</v>
+        <v>6582</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>376.0915053083323</v>
+        <v>376.3444454967211</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>98.5</v>
+        <v>31.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>38.89553809115606</v>
+        <v>49.97313150553244</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19.22926628807356</v>
+        <v>16.11337874704152</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4260270641207209</v>
+        <v>0.5924827903738391</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-1.739622495116524</v>
+        <v>0.0858805124822288</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6803</v>
+        <v>6588</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>375.9295961391885</v>
+        <v>376.0915053083323</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>262.5</v>
+        <v>98.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>34.6262886035513</v>
+        <v>38.89553810938283</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>23.580694955285</v>
+        <v>19.22926631040708</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.295474095009682</v>
+        <v>0.4260270641207209</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.2714874336048172</v>
+        <v>-1.739622495296783</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6642</v>
+        <v>6803</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>370.3845779602929</v>
+        <v>375.9295961391887</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>75.7</v>
+        <v>262.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>40.13628362551105</v>
+        <v>34.62628880053444</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>18.59929466878678</v>
+        <v>23.58069475178944</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.285703528019368</v>
+        <v>1.295474095009682</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.4384971379133551</v>
+        <v>-0.2714874343258844</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6581</v>
+        <v>6642</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>370.1575656479373</v>
+        <v>370.3845779602929</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>108.5</v>
+        <v>75.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>48.65731796388089</v>
+        <v>40.13628369354929</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.32780664506402</v>
+        <v>18.59929474230087</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.8699824923802491</v>
+        <v>1.285703528019368</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1035133429528306</v>
+        <v>-0.4384971378893142</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6807</v>
+        <v>6581</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>369.0688368309713</v>
+        <v>370.1575656479369</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>33.75</v>
+        <v>108.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>52.01042355311053</v>
+        <v>48.65731811294305</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.64816045544215</v>
+        <v>13.32780668229904</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5232780228463185</v>
+        <v>0.8699824923802491</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.6298689042743233</v>
+        <v>-0.1035133431931643</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6589</v>
+        <v>6807</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>354.7317166247609</v>
+        <v>369.0688368309714</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>49.35</v>
+        <v>33.75</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>45.89431680590722</v>
+        <v>52.01042355273218</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>20.5347609461226</v>
+        <v>11.64816050714527</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5656146918420226</v>
+        <v>0.5232780228463185</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.2867867952325379</v>
+        <v>0.6298689042863361</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6770</v>
+        <v>6589</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>350.2942830913144</v>
+        <v>354.7317166247609</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>67.5</v>
+        <v>49.35</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>40.15272520894131</v>
+        <v>45.89431687964704</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>12.87531439816044</v>
+        <v>20.53476104624207</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.544445684509364</v>
+        <v>0.5656146918420226</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.6310739031782974</v>
+        <v>-0.2867867952806088</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6695</v>
+        <v>6770</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>350.0154760015183</v>
+        <v>350.2942830913144</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>49.8</v>
+        <v>67.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45.9273251951744</v>
+        <v>40.15272524110595</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>22.15960265206066</v>
+        <v>12.87531454599219</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.5289195697530255</v>
+        <v>1.544445684509364</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.202552076534453</v>
+        <v>-0.63107390328646</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6698</v>
+        <v>6695</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>337.3668628545292</v>
+        <v>350.0154760015183</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>30.8</v>
+        <v>49.8</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>42.55848710857425</v>
+        <v>45.92732536253167</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>11.48764563415116</v>
+        <v>22.15960278942648</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>3.199977715953445</v>
+        <v>0.5289195697530255</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0956343457685689</v>
+        <v>-0.2025520768108499</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6597</v>
+        <v>6698</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>332.1511260848144</v>
+        <v>337.366862854529</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>73</v>
+        <v>30.8</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>53.1317280459363</v>
+        <v>42.55848719046357</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>7.168395358628843</v>
+        <v>11.48764569750837</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.043282731571084</v>
+        <v>3.199977715953445</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>1.203988343280925</v>
+        <v>-0.0956343459608443</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6680</v>
+        <v>6597</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>329.0064356636511</v>
+        <v>332.1511260848144</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>50.5</v>
+        <v>73</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.86727299817985</v>
+        <v>53.13172806538365</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>6.777896649125982</v>
+        <v>7.16839526569374</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.9630664034285163</v>
+        <v>1.043282731571084</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.7516372523201938</v>
+        <v>1.20398834234358</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, above_ichimoku_cloud</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6592</v>
+        <v>6680</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>327.9930522846715</v>
+        <v>329.0064356636511</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>56.5</v>
+        <v>50.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>34.51062884326615</v>
+        <v>51.86727334123461</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>33.5270170855535</v>
+        <v>6.777897298621363</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5799709404930738</v>
+        <v>0.9630664034285163</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0124056101871894</v>
+        <v>0.7516372362170046</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6579</v>
+        <v>6592</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>325.3201702109045</v>
+        <v>327.9930522846716</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>150</v>
+        <v>56.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>43.72292838778363</v>
+        <v>34.51062895261481</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>17.3217739361401</v>
+        <v>33.52701711827943</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.7109214221005739</v>
+        <v>0.5799709404930738</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.452702759247908</v>
+        <v>-0.0124056104756029</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6754</v>
+        <v>6579</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>321.5927511083673</v>
+        <v>325.3201702109045</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>52.72558970939033</v>
+        <v>43.72292848988235</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.95177989554759</v>
+        <v>17.32177404313823</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5117046607798984</v>
+        <v>0.7109214221005739</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.06537717036372689</v>
+        <v>-0.4527027598487537</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6558</v>
+        <v>6754</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>320.64665226509</v>
+        <v>321.5927511083673</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>23.85</v>
+        <v>42</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>40.71149695489823</v>
+        <v>52.72558965051051</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>23.36273642681659</v>
+        <v>14.95177989655883</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7487385006638612</v>
+        <v>0.5117046607798984</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0005529770199574</v>
+        <v>0.0653771702435524</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6486</v>
+        <v>6558</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>318.2272322314641</v>
+        <v>320.6466522650894</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>77.3</v>
+        <v>23.85</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>38.11514420193912</v>
+        <v>40.71149778787448</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>32.13628845969526</v>
+        <v>23.36273643774689</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.221246274916849</v>
+        <v>0.7487385006638612</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.5327728574300772</v>
+        <v>0.0005529765152295</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6719</v>
+        <v>6486</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>308.6791328859547</v>
+        <v>318.2272322314641</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>181</v>
+        <v>77.3</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>39.93123378511185</v>
+        <v>38.11514426751102</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>15.81989817582115</v>
+        <v>32.13628844088347</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.401380349387703</v>
+        <v>1.221246274916849</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.786289072995356</v>
+        <v>-0.5327728575262183</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6781</v>
+        <v>6719</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>307.4865261854988</v>
+        <v>308.6791328859546</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>981</v>
+        <v>181</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>38.30645663081737</v>
+        <v>39.93123396586415</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>10.49159890424658</v>
+        <v>15.81989842478769</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.620656557396836</v>
+        <v>1.401380349387703</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.006820844391207</v>
+        <v>0.7862890714331057</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6515</v>
+        <v>6781</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>305.7907276196478</v>
+        <v>307.4865261854988</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>5700</v>
+        <v>981</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,49 +5534,49 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>43.09823229165301</v>
+        <v>38.30645704005184</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>10.31828110954674</v>
+        <v>10.49159899942887</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6690605308605747</v>
+        <v>1.620656557396836</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-7.06269708193139</v>
+        <v>-0.0068208564084528</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6796</v>
+        <v>6515</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>305.3793375905204</v>
+        <v>305.7907276196479</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>55</v>
+        <v>5700</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,49 +5587,49 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>49.38123556405976</v>
+        <v>43.09823231228709</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>20.26358916404632</v>
+        <v>10.31828128922436</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5418511034759296</v>
+        <v>0.6690605308605747</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M97" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.6025456220083523</v>
+        <v>-7.062697102361028</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6494</v>
+        <v>6796</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>304.3116989117169</v>
+        <v>305.3793375905204</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>48.5</v>
+        <v>55</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>34.04496956022513</v>
+        <v>49.3812356016248</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>11.36809259033947</v>
+        <v>20.26358928408879</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.427815368266131</v>
+        <v>0.5418511034759296</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1589998471404625</v>
+        <v>0.6025456219602837</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6546</v>
+        <v>6494</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>301.0059018239601</v>
+        <v>304.3116989117146</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>60.5</v>
+        <v>48.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>48.73445713491957</v>
+        <v>34.0449695957047</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.23849863630789</v>
+        <v>11.36809266013442</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5095581050388197</v>
+        <v>1.427815368266131</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.267002474165094</v>
+        <v>-0.1589998471644926</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6732</v>
+        <v>6546</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>295.3613516716743</v>
+        <v>301.0059018239601</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>150.5</v>
+        <v>60.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>47.30896815081394</v>
+        <v>48.73445755703988</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.91525137579177</v>
+        <v>13.23849870330766</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.282829288401381</v>
+        <v>0.5095581050388197</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.4019348810240082</v>
+        <v>0.2670024733238796</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6739</v>
+        <v>6732</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>293.226458316404</v>
+        <v>295.3613516716743</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>991</v>
+        <v>150.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>39.61886137898453</v>
+        <v>47.30896856576809</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>10.25576792396881</v>
+        <v>17.91525143200357</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.866502353794811</v>
+        <v>1.282829288401381</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-13.0954677592119</v>
+        <v>0.401934879942468</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6788</v>
+        <v>6739</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>291.9151288371253</v>
+        <v>293.2264583164052</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>363</v>
+        <v>991</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,49 +5852,49 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>54.72431790151138</v>
+        <v>39.61886150287478</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>21.16454704797531</v>
+        <v>10.25576798146163</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.9825066716188792</v>
+        <v>0.866502353794811</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>3.365264012033677</v>
+        <v>-13.09546776642246</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6771</v>
+        <v>6788</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>285.7113769449716</v>
+        <v>291.9151288371256</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>41</v>
+        <v>363</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,49 +5905,49 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>38.87292478747723</v>
+        <v>54.72431806697826</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.91051766355571</v>
+        <v>21.16454704157488</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.2209081112722338</v>
+        <v>0.9825066716188792</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.1631685754667476</v>
+        <v>3.365264009029304</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6541</v>
+        <v>6771</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>283.1383309483253</v>
+        <v>285.7113769449714</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>30.35</v>
+        <v>41</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>42.45764922109622</v>
+        <v>38.87292477338803</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>21.33453374986884</v>
+        <v>17.91051767672893</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.715983579357133</v>
+        <v>0.2209081112722338</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.3551017619512979</v>
+        <v>-0.1631685755148195</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6679</v>
+        <v>6541</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>281.9130967416712</v>
+        <v>283.1383309483253</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>190.5</v>
+        <v>30.35</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>35.41509603367936</v>
+        <v>42.45764938878592</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.31238177857658</v>
+        <v>21.33453372127488</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.078502900528962</v>
+        <v>1.715983579357133</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.7794802609380953</v>
+        <v>0.3551017616388433</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6488</v>
+        <v>6679</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>278.3921373326332</v>
+        <v>281.9130967416714</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>1015</v>
+        <v>190.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>47.82990423176251</v>
+        <v>35.41509616109487</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>19.73279723490854</v>
+        <v>13.31238193404554</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.153750840951473</v>
+        <v>1.078502900528962</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>6.675569660120033</v>
+        <v>-0.7794802627406869</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6625</v>
+        <v>6488</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>275.4421509253306</v>
+        <v>278.392137332633</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>1015</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>38.31350463030076</v>
+        <v>47.82990424804738</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.27247860869487</v>
+        <v>19.73279719888867</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>2.687377642728104</v>
+        <v>1.153750840951473</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0619170188842497</v>
+        <v>6.675569659398874</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6573</v>
+        <v>6625</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>268.2200863779225</v>
+        <v>275.4421509253363</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>15.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>41.25928726583501</v>
+        <v>38.31350471932394</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>15.94183567838158</v>
+        <v>13.27247862608971</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.8299379167191434</v>
+        <v>2.687377642728104</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0062280318627836</v>
+        <v>0.0619170187640695</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6666</v>
+        <v>6573</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>261.6868156655027</v>
+        <v>268.2200863779226</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>41.8</v>
+        <v>15.7</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>27.59270499481987</v>
+        <v>41.25928683459671</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.0515010919943</v>
+        <v>15.94183563767772</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.965280789467224</v>
+        <v>0.8299379167191434</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.348825098130799</v>
+        <v>0.006228032127163</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6606</v>
+        <v>6666</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>253.3399354008218</v>
+        <v>261.6868156655026</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>24.05</v>
+        <v>41.8</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>38.03443872538384</v>
+        <v>27.59270531420654</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>31.13749711129635</v>
+        <v>18.05150127650618</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4974593191935302</v>
+        <v>1.965280789467224</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0637715721041256</v>
+        <v>-0.3488250989960446</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6761</v>
+        <v>6606</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>251.3391375442204</v>
+        <v>253.3399354008218</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>158.5</v>
+        <v>24.05</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>37.28838503904613</v>
+        <v>38.03443879139628</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>13.79468304035235</v>
+        <v>31.13749716131537</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.647220143220143</v>
+        <v>0.4974593191935302</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0123458448099644</v>
+        <v>-0.0637715721281627</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6477</v>
+        <v>6761</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>245.3705806221836</v>
+        <v>251.3391375442204</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>32.7</v>
+        <v>158.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>39.64088547268683</v>
+        <v>37.28838502306018</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.70003810665349</v>
+        <v>13.79468294468196</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.463532119626407</v>
+        <v>1.647220143220143</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.112495826833496</v>
+        <v>0.0123458446897704</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6692</v>
+        <v>6477</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>230.8528119928579</v>
+        <v>245.3705806221836</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>22.4</v>
+        <v>32.7</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>49.35259478869884</v>
+        <v>39.64088567146728</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>6.409023244170617</v>
+        <v>16.70003826326142</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.26719632735854</v>
+        <v>0.463532119626407</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0522079715998085</v>
+        <v>-0.1124958267734107</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6794</v>
+        <v>6692</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>229.8519214600232</v>
+        <v>230.852811992858</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>37.25311691363437</v>
+        <v>49.35259480769378</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.15631990385088</v>
+        <v>6.409023315723984</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.628982876404035</v>
+        <v>1.26719632735854</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.5096196669755979</v>
+        <v>0.0522079715277034</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6725</v>
+        <v>6794</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>229.5614283572856</v>
+        <v>229.851921460023</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>201.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>32.17364361827431</v>
+        <v>37.25311685751706</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.09496579432259</v>
+        <v>14.15631989642613</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>2.37332032106148</v>
+        <v>1.628982876404035</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0621584837921833</v>
+        <v>-0.5096196667352464</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6671</v>
+        <v>6725</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>224.7812343059879</v>
+        <v>229.5614283572855</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>22.65</v>
+        <v>201.5</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>42.06968442542752</v>
+        <v>32.17364410431519</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>15.98091826111581</v>
+        <v>16.09496582148293</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.130225142567373</v>
+        <v>2.37332032106148</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0017048242428463</v>
+        <v>-0.0621584849939242</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6651</v>
+        <v>6671</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>221.4660512473501</v>
+        <v>224.7812343059879</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>140</v>
+        <v>22.65</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>42.74231845826034</v>
+        <v>42.06968444236558</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15.61144951185245</v>
+        <v>15.98091796033679</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.6507962315458845</v>
+        <v>1.130225142567373</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-1.449683994802866</v>
+        <v>-0.0017048242909185</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6720</v>
+        <v>6651</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>199.0983476243518</v>
+        <v>221.4660512473501</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>99.3</v>
+        <v>140</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>37.43707044601851</v>
+        <v>42.74231848168809</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>15.07702928568361</v>
+        <v>15.61144949675886</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>3.30983476243518</v>
+        <v>0.6507962315458845</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-1.960102739464548</v>
+        <v>-1.449683994971109</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6624</v>
+        <v>6720</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>198.4018358751018</v>
+        <v>199.0983476243518</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>36.8</v>
+        <v>99.3</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>49.75314423757636</v>
+        <v>37.43707050335278</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>4.496964146270271</v>
+        <v>15.0770292560278</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.460649539614501</v>
+        <v>3.30983476243518</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>1</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.2118290964900894</v>
+        <v>-1.960102739825064</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6568</v>
+        <v>6624</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>182.009319259246</v>
+        <v>198.4018358751018</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>128.5</v>
+        <v>36.8</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>38.45095267158408</v>
+        <v>49.75314423656368</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>16.60653050277481</v>
+        <v>4.496964147950078</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.8480209587845767</v>
+        <v>1.460649539614501</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-1.462824847416794</v>
+        <v>-0.2118290964900894</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6512</v>
+        <v>6568</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>173.5823119907919</v>
+        <v>182.009319259246</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>0</v>
+        <v>128.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>39.05662274927356</v>
+        <v>38.45095278770568</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>9.038901619851687</v>
+        <v>16.60653063810565</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.0366029020872369</v>
+        <v>0.8480209587845767</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-1.174730467019757</v>
+        <v>-1.462824848258027</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6753</v>
+        <v>6512</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>171.3097086293172</v>
+        <v>173.5823119907919</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>31.2303960913115</v>
+        <v>39.05662275300025</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>13.85500157484347</v>
+        <v>9.038901694804199</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.229451563057403</v>
+        <v>0.0366029020872369</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,62 +6930,115 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.4229973462175929</v>
+        <v>-1.174730467091859</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
+        <v>6753</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>龍德造船</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>171.3097086293172</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>31.23039637363044</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>13.85500163288504</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>1.229451563057403</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>-0.4229973471790029</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
         <v>6552</v>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>易華電</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D123" s="2" t="n">
-        <v>100.7326657700753</v>
-      </c>
-      <c r="E123" s="2" t="n">
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>100.7326657700751</v>
+      </c>
+      <c r="E124" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>36.9022315348828</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>16.90726025054166</v>
-      </c>
-      <c r="J123" s="2" t="n">
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>36.90223202853276</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>16.907260260068</v>
+      </c>
+      <c r="J124" s="2" t="n">
         <v>1.264622346314928</v>
       </c>
-      <c r="K123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N123" s="2" t="n">
-        <v>-0.0512442701921804</v>
-      </c>
-      <c r="O123" s="2" t="inlineStr">
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>-0.0512442706248018</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
